--- a/Big_Data/Taller_2/Actividad1.xlsx
+++ b/Big_Data/Taller_2/Actividad1.xlsx
@@ -58,8 +58,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -75,7 +83,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -83,12 +91,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -387,13 +413,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -573,13 +599,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -759,13 +785,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -945,13 +971,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1131,13 +1157,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1317,13 +1343,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1503,13 +1529,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1689,13 +1715,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1875,13 +1901,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2061,13 +2087,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2247,13 +2273,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2433,13 +2459,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2619,13 +2645,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2805,13 +2831,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2991,13 +3017,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3177,13 +3203,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3363,13 +3389,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3549,13 +3575,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3735,13 +3761,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3921,13 +3947,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4107,13 +4133,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4293,13 +4319,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4479,13 +4505,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4665,13 +4691,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4851,13 +4877,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -5037,13 +5063,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -5223,13 +5249,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -5409,13 +5435,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -5595,13 +5621,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -5781,13 +5807,13 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
